--- a/rf-data/TestData.xlsx
+++ b/rf-data/TestData.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automationexercise_RF\rf-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9560DDD-7985-4C12-868E-36C08BC5C61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A39418-0585-4AAE-898C-D3E648D50AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
+    <sheet name="Kombocart" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>TCID</t>
   </si>
@@ -55,6 +56,81 @@
   </si>
   <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>Column4</t>
+  </si>
+  <si>
+    <t>Column5</t>
+  </si>
+  <si>
+    <t>Column6</t>
+  </si>
+  <si>
+    <t>Column7</t>
+  </si>
+  <si>
+    <t>Column8</t>
+  </si>
+  <si>
+    <t>Column9</t>
+  </si>
+  <si>
+    <t>Column10</t>
+  </si>
+  <si>
+    <t>Column11</t>
+  </si>
+  <si>
+    <t>Column12</t>
+  </si>
+  <si>
+    <t>Column13</t>
+  </si>
+  <si>
+    <t>Column14</t>
+  </si>
+  <si>
+    <t>Column15</t>
+  </si>
+  <si>
+    <t>Column16</t>
+  </si>
+  <si>
+    <t>Column17</t>
+  </si>
+  <si>
+    <t>Column18</t>
+  </si>
+  <si>
+    <t>Column19</t>
+  </si>
+  <si>
+    <t>Column20</t>
+  </si>
+  <si>
+    <t>Column21</t>
+  </si>
+  <si>
+    <t>Column22</t>
+  </si>
+  <si>
+    <t>Column23</t>
+  </si>
+  <si>
+    <t>K01</t>
+  </si>
+  <si>
+    <t>Validate Logo</t>
   </si>
 </sst>
 </file>
@@ -108,6 +184,41 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FEFACEB6-F5A0-4226-88AB-E66276CDBE01}" name="Table1" displayName="Table1" ref="A1:Z11" totalsRowShown="0">
+  <autoFilter ref="A1:Z11" xr:uid="{FEFACEB6-F5A0-4226-88AB-E66276CDBE01}"/>
+  <tableColumns count="26">
+    <tableColumn id="1" xr3:uid="{28D52F7C-0EB2-44B1-BDA6-ABA1139565DC}" name="TCID"/>
+    <tableColumn id="2" xr3:uid="{8FC2AC4C-9C09-44E6-8062-F60B9C88E3FB}" name="TestcaseName"/>
+    <tableColumn id="3" xr3:uid="{BD4F3273-4D43-4536-8222-A9F6A6ED418C}" name="Execution"/>
+    <tableColumn id="4" xr3:uid="{B8C384E9-6EE1-42A8-9F13-212DAD69FF4C}" name="Column1"/>
+    <tableColumn id="5" xr3:uid="{A8958C01-1D33-40BD-9685-BC9D4B31FF9A}" name="Column2"/>
+    <tableColumn id="6" xr3:uid="{CA690708-ED59-4D98-B7EF-6B72771CB64A}" name="Column3"/>
+    <tableColumn id="7" xr3:uid="{48C0A585-E449-4A11-9E8F-3501C226140D}" name="Column4"/>
+    <tableColumn id="8" xr3:uid="{20EBD8BB-F75F-41E9-A7EA-28E31D48453A}" name="Column5"/>
+    <tableColumn id="9" xr3:uid="{1995C530-1F31-47EF-B872-88650B9EE232}" name="Column6"/>
+    <tableColumn id="10" xr3:uid="{8C043093-F965-4DCE-9372-7531E7965035}" name="Column7"/>
+    <tableColumn id="11" xr3:uid="{1CEBA686-A272-47A3-B647-4539844B54CE}" name="Column8"/>
+    <tableColumn id="12" xr3:uid="{5C4552DC-35E8-4307-8679-8871312ABE29}" name="Column9"/>
+    <tableColumn id="13" xr3:uid="{7B79DA0E-D4F7-4B92-9EC9-6D07C5B23921}" name="Column10"/>
+    <tableColumn id="14" xr3:uid="{61FD75C6-A0AD-4EF6-8C0E-BCE6980A8093}" name="Column11"/>
+    <tableColumn id="15" xr3:uid="{20C7796E-11F3-4745-A3DB-0DDEF8A4F041}" name="Column12"/>
+    <tableColumn id="16" xr3:uid="{686A12DD-CEA8-4E29-A10B-339491E79132}" name="Column13"/>
+    <tableColumn id="17" xr3:uid="{F3D63E26-4605-4527-A5F1-3CCE235CF8EA}" name="Column14"/>
+    <tableColumn id="18" xr3:uid="{368A9DCE-E004-4CFE-92E8-98D3DBDB5C46}" name="Column15"/>
+    <tableColumn id="19" xr3:uid="{92486073-C7F0-4CCB-86BA-97FCBD389A08}" name="Column16"/>
+    <tableColumn id="20" xr3:uid="{E8D2064D-2BDA-4047-ACA1-A04DC881E02F}" name="Column17"/>
+    <tableColumn id="21" xr3:uid="{2F0A0FE3-27CD-4C32-995F-A14E278CCF95}" name="Column18"/>
+    <tableColumn id="22" xr3:uid="{5AEB4F03-34AA-4051-B7B9-2EB1F7447E07}" name="Column19"/>
+    <tableColumn id="23" xr3:uid="{6C3D4C7E-3B7F-4D65-B15B-9FDCDEBEE726}" name="Column20"/>
+    <tableColumn id="24" xr3:uid="{93FF2F80-5DF1-478B-8578-B85499573AF3}" name="Column21"/>
+    <tableColumn id="25" xr3:uid="{ED235928-0698-432D-AB64-FF93B1425486}" name="Column22"/>
+    <tableColumn id="26" xr3:uid="{D4A36470-0D06-4B37-A0DB-C5C4B9E2DF73}" name="Column23"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,4 +528,115 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{547C47FB-9C70-4311-A5CD-C3B9EF315C65}">
+  <dimension ref="A1:Z2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="12" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="26" width="11.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" t="s">
+        <v>28</v>
+      </c>
+      <c r="W1" t="s">
+        <v>29</v>
+      </c>
+      <c r="X1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>